--- a/0_SELECT_ZIVE_DATA_2023/AnotacijosLogai/10_Anotacijos_logai/10_Anotavimo_logas.xlsx
+++ b/0_SELECT_ZIVE_DATA_2023/AnotacijosLogai/10_Anotacijos_logai/10_Anotavimo_logas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\kesju\DI\2025_ZIVEO\PROJECT_TRAIN_UNET\0_SELECT_ZIVE_DATA_2023\AnotacijosLogai\10_Anotacijos_logai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7AEB874-467A-45B1-A4D5-4C9EDCD5B7FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00EA92FC-9C13-4976-AFA9-F14600559575}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -740,7 +740,7 @@
       <c r="D2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="4" t="b">
+      <c r="F2" s="4" t="b">
         <v>1</v>
       </c>
       <c r="G2" s="3"/>
@@ -776,7 +776,7 @@
       <c r="D3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="4" t="b">
+      <c r="F3" s="4" t="b">
         <v>1</v>
       </c>
       <c r="G3" s="3"/>
@@ -810,7 +810,7 @@
       <c r="D4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="4" t="b">
+      <c r="F4" s="4" t="b">
         <v>1</v>
       </c>
       <c r="G4" s="3"/>
@@ -842,7 +842,7 @@
       <c r="D5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="4" t="b">
+      <c r="F5" s="4" t="b">
         <v>1</v>
       </c>
       <c r="G5" s="3"/>
@@ -876,7 +876,7 @@
       <c r="D6" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="4" t="b">
+      <c r="F6" s="4" t="b">
         <v>1</v>
       </c>
       <c r="G6" s="3" t="s">
@@ -912,7 +912,7 @@
       <c r="D7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="4" t="b">
+      <c r="F7" s="4" t="b">
         <v>1</v>
       </c>
       <c r="G7" s="3"/>
@@ -946,7 +946,7 @@
       <c r="D8" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="4" t="b">
+      <c r="F8" s="4" t="b">
         <v>1</v>
       </c>
       <c r="G8" s="3" t="s">
@@ -982,7 +982,7 @@
       <c r="D9" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="4" t="b">
+      <c r="F9" s="4" t="b">
         <v>1</v>
       </c>
       <c r="G9" s="3"/>
@@ -1003,7 +1003,7 @@
       <c r="D10" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="4" t="b">
+      <c r="F10" s="4" t="b">
         <v>1</v>
       </c>
       <c r="G10" s="3" t="s">
@@ -1026,7 +1026,7 @@
       <c r="D11" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="4" t="b">
+      <c r="F11" s="4" t="b">
         <v>1</v>
       </c>
       <c r="G11" s="8"/>

--- a/0_SELECT_ZIVE_DATA_2023/AnotacijosLogai/10_Anotacijos_logai/10_Anotavimo_logas.xlsx
+++ b/0_SELECT_ZIVE_DATA_2023/AnotacijosLogai/10_Anotacijos_logai/10_Anotavimo_logas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\kesju\DI\2025_ZIVEO\PROJECT_TRAIN_UNET\0_SELECT_ZIVE_DATA_2023\AnotacijosLogai\10_Anotacijos_logai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00EA92FC-9C13-4976-AFA9-F14600559575}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4545248E-2E17-47E0-9195-4D921DE2969D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -882,7 +882,9 @@
       <c r="G6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H6" s="4"/>
+      <c r="H6" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
       <c r="K6" s="12" t="s">
@@ -952,7 +954,9 @@
       <c r="G8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H8" s="4"/>
+      <c r="H8" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
       <c r="K8" s="12" t="s">
@@ -1009,7 +1013,9 @@
       <c r="G10" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H10" s="8"/>
+      <c r="H10" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="I10" s="8"/>
       <c r="J10" s="8"/>
     </row>

--- a/0_SELECT_ZIVE_DATA_2023/AnotacijosLogai/10_Anotacijos_logai/10_Anotavimo_logas.xlsx
+++ b/0_SELECT_ZIVE_DATA_2023/AnotacijosLogai/10_Anotacijos_logai/10_Anotavimo_logas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\kesju\DI\2025_ZIVEO\PROJECT_TRAIN_UNET\0_SELECT_ZIVE_DATA_2023\AnotacijosLogai\10_Anotacijos_logai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4545248E-2E17-47E0-9195-4D921DE2969D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63B62024-8615-454D-B5A5-524AA8C7C02D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -882,10 +882,9 @@
       <c r="G6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H6" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="I6" s="4"/>
+      <c r="I6" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="J6" s="4"/>
       <c r="K6" s="12" t="s">
         <v>15</v>
@@ -954,10 +953,9 @@
       <c r="G8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H8" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="I8" s="4"/>
+      <c r="I8" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="J8" s="4"/>
       <c r="K8" s="12" t="s">
         <v>15</v>
@@ -1013,10 +1011,9 @@
       <c r="G10" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H10" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" s="8"/>
+      <c r="I10" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="J10" s="8"/>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.35">
